--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260902.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.68%</t>
+          <t>10.63%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.18%</t>
+          <t>10.40%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.13%</t>
+          <t>8.11%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.63%</t>
+          <t>7.58%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.67%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.38%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.48%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.71%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1100,95 +1100,95 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>47,127</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>47,127</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,310</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>51,310</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,22 +1305,22 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1371,44 +1371,44 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MYRG US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MYR集團公司</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,651</t>
+          <t>5,878</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>MYRG US</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>MYR集團公司</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,878</t>
+          <t>3,651</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>118,600,292</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
